--- a/templates/33-prioritisation-template.xlsx
+++ b/templates/33-prioritisation-template.xlsx
@@ -2,8 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="Blank template" sheetId="2" r:id="rId2"/>
+    <sheet name="Blank template" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -448,114 +447,6 @@
   </sheetPr>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="92" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10.33  Prioritisation</t>
-        </is>
-      </c>
-      <c r="B1" s="5"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Planning, governance and tracking</t>
-        </is>
-      </c>
-      <c r="B2" s="8"/>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">What it is for</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Orders requirements or work against agreed bases such as value, cost, risk, dependency, regulatory deadline or implementation difficulty.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reach for it when</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reach for it whenever demand exceeds capacity, which is nearly always, and the sequence has to be defensible to people who lose out.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Confused with</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prioritisation orders things you intend to do; decision analysis picks between options where some are discarded. Also watch the basis: an item where a regulatory date is in play is not decided by value.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tasks</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5.3 Prioritize Requirements  ·  5.4 Assess Requirements Changes  ·  6.4 Define Change Strategy</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Knowledge areas</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5, 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The blank template is on the next sheet — fill it in.</t>
-        </is>
-      </c>
-      <c r="B10" s="6"/>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A10:B10"/>
-  </mergeCells>
-  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
